--- a/docs/dossiers/dossier-paris-20-84db089c.xlsx
+++ b/docs/dossiers/dossier-paris-20-84db089c.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 20/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 21/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20-84db089c.xlsx
+++ b/docs/dossiers/dossier-paris-20-84db089c.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 21/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 22/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20-84db089c.xlsx
+++ b/docs/dossiers/dossier-paris-20-84db089c.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 22/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 23/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20-84db089c.xlsx
+++ b/docs/dossiers/dossier-paris-20-84db089c.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 23/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 24/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20-84db089c.xlsx
+++ b/docs/dossiers/dossier-paris-20-84db089c.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 24/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 25/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20-84db089c.xlsx
+++ b/docs/dossiers/dossier-paris-20-84db089c.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 25/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 26/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="B11" s="29" t="inlineStr">
         <is>
-          <t>loyer_estime · rendement_sous_objectif</t>
+          <t>loyer_estime · rendement_sous_objectif · occupation_a_confirmer</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20-84db089c.xlsx
+++ b/docs/dossiers/dossier-paris-20-84db089c.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Annonce" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Synthèse'!$A$1:$C$58</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Synthèse'!$A$1:$C$59</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -793,7 +793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="B8" s="10">
-        <f>B25</f>
+        <f>B26</f>
         <v/>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="F8" s="8">
-        <f>B38-(B43+B44+B45)/12</f>
+        <f>B39-(B44+B45+B46)/12</f>
         <v/>
       </c>
     </row>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="B9" s="10">
-        <f>B36</f>
+        <f>B37</f>
         <v/>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="F9" s="8">
-        <f>B49</f>
+        <f>B50</f>
         <v/>
       </c>
     </row>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="B10" s="11">
-        <f>B38</f>
+        <f>B39</f>
         <v/>
       </c>
     </row>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="B11" s="11">
-        <f>B49</f>
+        <f>B50</f>
         <v/>
       </c>
     </row>
@@ -922,14 +922,14 @@
         </is>
       </c>
       <c r="B12" s="12">
-        <f>B54</f>
+        <f>B55</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 5,34 % sur 20 ans, charges provisionnées), il reste environ 465 €/mois à financer en plus du loyer — marge de négociation ou apport supplémentaire à prévoir.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 5,34 % sur 20 ans, charges provisionnées), il reste environ 289 €/mois à financer en plus du loyer — marge de négociation ou apport supplémentaire à prévoir.</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="B18" s="17" t="n">
-        <v>365000</v>
+        <v>335000</v>
       </c>
     </row>
     <row r="19">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="C21" s="19" t="inlineStr">
         <is>
-          <t>ce bien est 23 % au-dessus de la médiane locale</t>
+          <t>ce bien est 12 % au-dessus de la médiane locale</t>
         </is>
       </c>
     </row>
@@ -1033,364 +1033,381 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>Évolution du prix demandé</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>365 000 € (23/08) → 335 000 € (26/10)  —  −8.2 % depuis la première vue</t>
+        </is>
+      </c>
+      <c r="C23" s="19" t="inlineStr">
+        <is>
+          <t>un prix qui baisse est un levier de négociation documenté</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>HYPOTHÈSES — cellules jaunes à ajuster avec votre conseiller</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>Prix négocié retenu</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="n">
-        <v>365000</v>
-      </c>
-      <c r="C25" s="19" t="inlineStr">
-        <is>
-          <t>par défaut le prix affiché — un prix demandé se négocie</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>Frais d'acquisition (notaire, garanties)</t>
-        </is>
-      </c>
-      <c r="B26" s="20" t="n">
-        <v>0.08</v>
+          <t>Prix négocié retenu</t>
+        </is>
+      </c>
+      <c r="B26" s="18" t="n">
+        <v>335000</v>
+      </c>
+      <c r="C26" s="19" t="inlineStr">
+        <is>
+          <t>par défaut le prix affiché — un prix demandé se négocie</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
         <is>
-          <t>Apport personnel</t>
+          <t>Frais d'acquisition (notaire, garanties)</t>
         </is>
       </c>
       <c r="B27" s="20" t="n">
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>Taux du crédit (hors assurance)</t>
+          <t>Apport personnel</t>
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.0534</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
-          <t>Durée du crédit (années)</t>
-        </is>
-      </c>
-      <c r="B29" s="21" t="n">
-        <v>20</v>
+          <t>Taux du crédit (hors assurance)</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="n">
+        <v>0.0534</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>Taxe foncière (en mois de loyer par an)</t>
-        </is>
-      </c>
-      <c r="B30" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" s="19" t="inlineStr">
-        <is>
-          <t>à remplacer par le montant réel dès que connu</t>
-        </is>
+          <t>Durée du crédit (années)</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
-          <t>Provision entretien &amp; vacance (% du loyer)</t>
-        </is>
-      </c>
-      <c r="B31" s="20" t="n">
-        <v>0.05</v>
+          <t>Taxe foncière (en mois de loyer par an)</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="19" t="inlineStr">
+        <is>
+          <t>à remplacer par le montant réel dès que connu</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
+          <t>Provision entretien &amp; vacance (% du loyer)</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
           <t>Assurance propriétaire (PNO, €/an)</t>
         </is>
       </c>
-      <c r="B32" s="18" t="n">
+      <c r="B33" s="18" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>PLAN DE FINANCEMENT</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="14" t="inlineStr">
-        <is>
-          <t>Coût d'acquisition total</t>
-        </is>
-      </c>
-      <c r="B35" s="17">
-        <f>B25*(1+B26)</f>
-        <v/>
-      </c>
-      <c r="C35" s="19" t="inlineStr">
-        <is>
-          <t>prix négocié + frais d'acquisition</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
         <is>
-          <t>Apport personnel</t>
+          <t>Coût d'acquisition total</t>
         </is>
       </c>
       <c r="B36" s="17">
-        <f>B35*B27</f>
-        <v/>
+        <f>B26*(1+B27)</f>
+        <v/>
+      </c>
+      <c r="C36" s="19" t="inlineStr">
+        <is>
+          <t>prix négocié + frais d'acquisition</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
         <is>
-          <t>Montant emprunté</t>
+          <t>Apport personnel</t>
         </is>
       </c>
       <c r="B37" s="17">
-        <f>B35-B36</f>
+        <f>B36*B28</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>Mensualité du crédit</t>
-        </is>
-      </c>
-      <c r="B38" s="23">
-        <f>IFERROR(-PMT(B28/12,B29*12,B37),0)</f>
+          <t>Montant emprunté</t>
+        </is>
+      </c>
+      <c r="B38" s="17">
+        <f>B36-B37</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
         <is>
+          <t>Mensualité du crédit</t>
+        </is>
+      </c>
+      <c r="B39" s="23">
+        <f>IFERROR(-PMT(B29/12,B30*12,B38),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
           <t>Service de la dette (annuel)</t>
         </is>
       </c>
-      <c r="B39" s="17">
-        <f>B38*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="7" t="inlineStr">
+      <c r="B40" s="17">
+        <f>B39*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>EXPLOITATION ANNUELLE</t>
         </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="14" t="inlineStr">
-        <is>
-          <t>Loyers annuels HT</t>
-        </is>
-      </c>
-      <c r="B42" s="17">
-        <f>IFERROR(B20*12,0)</f>
-        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
-          <t>− Taxe foncière</t>
+          <t>Loyers annuels HT</t>
         </is>
       </c>
       <c r="B43" s="17">
-        <f>-IFERROR(B20*B30,0)</f>
+        <f>IFERROR(B20*12,0)</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>− Entretien &amp; vacance locative</t>
+          <t>− Taxe foncière</t>
         </is>
       </c>
       <c r="B44" s="17">
-        <f>-B42*B31</f>
+        <f>-IFERROR(B20*B31,0)</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="14" t="inlineStr">
         <is>
-          <t>− Assurance PNO</t>
+          <t>− Entretien &amp; vacance locative</t>
         </is>
       </c>
       <c r="B45" s="17">
-        <f>-B32</f>
+        <f>-B43*B32</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>Revenu net avant crédit</t>
+          <t>− Assurance PNO</t>
         </is>
       </c>
       <c r="B46" s="17">
-        <f>B42+B43+B44+B45</f>
+        <f>-B33</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="14" t="inlineStr">
         <is>
-          <t>− Remboursement du crédit</t>
+          <t>Revenu net avant crédit</t>
         </is>
       </c>
       <c r="B47" s="17">
-        <f>-B39</f>
+        <f>B43+B44+B45+B46</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>Cash-flow annuel</t>
+          <t>− Remboursement du crédit</t>
         </is>
       </c>
       <c r="B48" s="17">
-        <f>B46-B39</f>
+        <f>-B40</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="14" t="inlineStr">
         <is>
+          <t>Cash-flow annuel</t>
+        </is>
+      </c>
+      <c r="B49" s="17">
+        <f>B47-B40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="14" t="inlineStr">
+        <is>
           <t>Cash-flow mensuel</t>
         </is>
       </c>
-      <c r="B49" s="24">
-        <f>B48/12</f>
-        <v/>
-      </c>
-      <c r="C49" s="19" t="inlineStr">
+      <c r="B50" s="24">
+        <f>B49/12</f>
+        <v/>
+      </c>
+      <c r="C50" s="19" t="inlineStr">
         <is>
           <t>positif : le bien se paie tout seul, loyer ≥ crédit + charges</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="7" t="inlineStr">
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>LES RATIOS QUE REGARDE LE BANQUIER</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="14" t="inlineStr">
-        <is>
-          <t>Rendement brut</t>
-        </is>
-      </c>
-      <c r="B52" s="25">
-        <f>IFERROR(B42/B25,"")</f>
-        <v/>
-      </c>
-      <c r="C52" s="19" t="inlineStr">
-        <is>
-          <t>loyer annuel ÷ prix — la base de comparaison des biens</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="14" t="inlineStr">
         <is>
-          <t>Rendement net avant crédit</t>
+          <t>Rendement brut</t>
         </is>
       </c>
       <c r="B53" s="25">
-        <f>IFERROR(B46/B35,"")</f>
+        <f>IFERROR(B43/B26,"")</f>
         <v/>
       </c>
       <c r="C53" s="19" t="inlineStr">
         <is>
-          <t>après taxe foncière, entretien et assurance</t>
+          <t>loyer annuel ÷ prix — la base de comparaison des biens</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>DSCR — couverture de la dette</t>
-        </is>
-      </c>
-      <c r="B54" s="26">
-        <f>IFERROR(B46/B39,"")</f>
+          <t>Rendement net avant crédit</t>
+        </is>
+      </c>
+      <c r="B54" s="25">
+        <f>IFERROR(B47/B36,"")</f>
         <v/>
       </c>
       <c r="C54" s="19" t="inlineStr">
         <is>
-          <t>revenu net ÷ crédit : ≥ 1,20 rassure une banque</t>
+          <t>après taxe foncière, entretien et assurance</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
         <is>
-          <t>LTV — part financée par la banque</t>
-        </is>
-      </c>
-      <c r="B55" s="25">
-        <f>IFERROR(B37/B25,"")</f>
+          <t>DSCR — couverture de la dette</t>
+        </is>
+      </c>
+      <c r="B55" s="26">
+        <f>IFERROR(B47/B40,"")</f>
         <v/>
       </c>
       <c r="C55" s="19" t="inlineStr">
         <is>
-          <t>≤ 80 % est la zone de confort bancaire</t>
+          <t>revenu net ÷ crédit : ≥ 1,20 rassure une banque</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
         <is>
-          <t>Effort d'épargne mensuel si négatif</t>
-        </is>
-      </c>
-      <c r="B56" s="23">
-        <f>MAX(0,-B48/12)</f>
-        <v/>
+          <t>LTV — part financée par la banque</t>
+        </is>
+      </c>
+      <c r="B56" s="25">
+        <f>IFERROR(B38/B26,"")</f>
+        <v/>
+      </c>
+      <c r="C56" s="19" t="inlineStr">
+        <is>
+          <t>≤ 80 % est la zone de confort bancaire</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="14" t="inlineStr">
         <is>
+          <t>Effort d'épargne mensuel si négatif</t>
+        </is>
+      </c>
+      <c r="B57" s="23">
+        <f>MAX(0,-B49/12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="14" t="inlineStr">
+        <is>
           <t>Score de l'outil de veille</t>
         </is>
       </c>
-      <c r="B57" s="15" t="inlineStr">
-        <is>
-          <t>61/100</t>
-        </is>
-      </c>
-      <c r="C57" s="19" t="inlineStr">
+      <c r="B58" s="15" t="inlineStr">
+        <is>
+          <t>66/100</t>
+        </is>
+      </c>
+      <c r="C58" s="19" t="inlineStr">
         <is>
           <t>rendement, emplacement, prix vs marché, financement, fiscalité</t>
         </is>
@@ -1399,18 +1416,18 @@
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A42:C42"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A13:C14"/>
-    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:C35"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A24:C24"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A52:C52"/>
   </mergeCells>
-  <conditionalFormatting sqref="B48">
+  <conditionalFormatting sqref="B49">
     <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -1418,7 +1435,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B49">
+  <conditionalFormatting sqref="B50">
     <cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -1426,7 +1443,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B54">
+  <conditionalFormatting sqref="B55">
     <cfRule type="cellIs" priority="5" operator="greaterThanOrEqual" dxfId="0">
       <formula>1.2</formula>
     </cfRule>
@@ -1503,7 +1520,7 @@
         </is>
       </c>
       <c r="G1">
-        <f>'Synthèse'!B29</f>
+        <f>'Synthèse'!B30</f>
         <v/>
       </c>
     </row>
@@ -1512,7 +1529,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="8">
-        <f>IF(A2&lt;=$G$1,'Synthèse'!$B$37,"")</f>
+        <f>IF(A2&lt;=$G$1,'Synthèse'!$B$38,"")</f>
         <v/>
       </c>
       <c r="C2" s="8">
@@ -1533,7 +1550,7 @@
         </is>
       </c>
       <c r="G2">
-        <f>'Synthèse'!B28</f>
+        <f>'Synthèse'!B29</f>
         <v/>
       </c>
     </row>
@@ -1558,7 +1575,7 @@
         <v/>
       </c>
       <c r="G3">
-        <f>'Synthèse'!B39</f>
+        <f>'Synthèse'!B40</f>
         <v/>
       </c>
     </row>
@@ -2261,7 +2278,7 @@
       </c>
       <c r="B8" s="29" t="inlineStr">
         <is>
-          <t>stable depuis la première vue</t>
+          <t>365 000 € (23/08) → 335 000 € (26/10)  —  −8.2 % depuis la première vue</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2314,7 @@
       </c>
       <c r="B11" s="29" t="inlineStr">
         <is>
-          <t>loyer_estime · rendement_sous_objectif · occupation_a_confirmer</t>
+          <t>loyer_estime · occupation_a_confirmer</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20-84db089c.xlsx
+++ b/docs/dossiers/dossier-paris-20-84db089c.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 26/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 27/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>66/100</t>
+          <t>62/100</t>
         </is>
       </c>
       <c r="C58" s="19" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="B12" s="29" t="inlineStr">
         <is>
-          <t>Bien Commercial À Vendre. RUE DES PYRENEES - VILLAGE JOURDAIN Commerce à vendre — murs, idéalement situé dans un quartier commerçant animé du village …</t>
+          <t>Bien Commercial À Vendre. RUE DES PYRENEES - VILLAGE JOURDAIN MURS DE BOUTIQUE ET POSSIBILITE DE LOGEMENT , idéalement situé dans un quartier commerç …</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20-84db089c.xlsx
+++ b/docs/dossiers/dossier-paris-20-84db089c.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 27/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 28/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 5,34 % sur 20 ans, charges provisionnées), il reste environ 289 €/mois à financer en plus du loyer — marge de négociation ou apport supplémentaire à prévoir.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 5,34 % sur 20 ans, charges provisionnées), il reste environ 241 €/mois à financer en plus du loyer — marge de négociation ou apport supplémentaire à prévoir.</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="B20" s="18" t="n">
-        <v>1962.22</v>
+        <v>2018.28</v>
       </c>
       <c r="C20" s="19" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>62/100</t>
+          <t>64/100</t>
         </is>
       </c>
       <c r="C58" s="19" t="inlineStr">

--- a/docs/dossiers/dossier-paris-20-84db089c.xlsx
+++ b/docs/dossiers/dossier-paris-20-84db089c.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 28/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 29/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 5,34 % sur 20 ans, charges provisionnées), il reste environ 241 €/mois à financer en plus du loyer — marge de négociation ou apport supplémentaire à prévoir.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 5,34 % sur 20 ans, charges provisionnées), il reste environ 192 €/mois à financer en plus du loyer — marge de négociation ou apport supplémentaire à prévoir.</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="B20" s="18" t="n">
-        <v>2018.28</v>
+        <v>2074.34</v>
       </c>
       <c r="C20" s="19" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>64/100</t>
+          <t>66/100</t>
         </is>
       </c>
       <c r="C58" s="19" t="inlineStr">

--- a/docs/dossiers/dossier-paris-20-84db089c.xlsx
+++ b/docs/dossiers/dossier-paris-20-84db089c.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 29/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 30/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-20-84db089c.xlsx
+++ b/docs/dossiers/dossier-paris-20-84db089c.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 30/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 31/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
